--- a/PTBR/Lang/PTBR/Dialog/Drama/ashland.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/ashland.xlsx
@@ -569,9 +569,9 @@
           <t>Good to see your face again. How is the development of the base going?</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Fico feliz em ver seu rosto novamente. O desenvolvimento da base está progredindo bem?</t>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>Bom ver sua cara de novo. Como anda o desenvolvimento da base?</t>
         </is>
       </c>
     </row>
@@ -599,9 +599,9 @@
           <t>How is life in Tyris treating you? It's a good idea to venture out sometimes and visit towns in various reigions.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Você já se acostumou com a vida em Tyris? De vez em quando, vale a pena fazer uma viagem e visitar cidades em diferentes regiões.</t>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>Como a vida em Tyris está te tratando? É uma boa ideia se aventurar de vez em quando e visitar cidades em várias regiões.</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
 I'm Ashland, on our way to the royal capital of Palmia with my companion. You aren't from around here, are you? I suppose I could spare some time to teach you the way of living in this land before we part. If you wish, of course.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Parece que você já pode se mover sem problemas.
-Eu sou Ashland. Estou a caminho da capital, Palmia, com um acompanhante por um determinado motivo. Pelo visto, você não conhece muito bem esta região. Talvez eu possa te passar algumas dicas de vida até retomarmos nossa jornada. Claro, se você desejar.</t>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>Então parece que você está inteiro.
+Sou Ashland, a caminho da capital real de Palmia com minha companheira. Você não é daqui, né? Acho que posso arranjar um tempo para te ensinar o jeito de viver nesta terra antes de partirmos. Se quiser, claro.</t>
         </is>
       </c>
     </row>
@@ -666,9 +666,9 @@
           <t>What is the land deed?</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>O que é a escritura de propriedade?</t>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>O que é a escritura de terra?</t>
         </is>
       </c>
     </row>
@@ -701,9 +701,9 @@
           <t>What is my goal?</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Qual é o objetivo da colonização?</t>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>Qual é o meu objetivo?</t>
         </is>
       </c>
     </row>
@@ -731,9 +731,9 @@
           <t>Teach me the way of living.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Quero que me ensine algumas dicas de vida.</t>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>Me ensine o jeito de viver.</t>
         </is>
       </c>
     </row>
@@ -761,9 +761,9 @@
           <t>I have some questions.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Tenho algo que gostaria de perguntar.</t>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>Tenho algumas perguntas.</t>
         </is>
       </c>
     </row>
@@ -833,14 +833,12 @@
 Don't worry about it, it's just my quota. Although a deed for land sounds like a good thing to have, I doubt if anyone gives a damn these days. Throw it to the bonfire if you like, for all I care. </t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você está se sentindo um pouco melhor?_x000D_
-_x000D_
-Primeiro de tudo, você ganhou isso._x000D_
-(O homem lhe lança um pedaço de pergaminho.)_x000D_
-_x000D_
-Não se preocupe com isso, é apenas a minha cota. Embora uma escritura de terra pareça algo bom de se ter, duvido que alguém dê a mínima atualmente. Jogue-a na fogueira se quiser, tanto faz para mim. </t>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Está se sentindo um pouco melhor?
+Primeiro de tudo, você ganhou isto.
+(O homem te joga um pedaço de pergaminho.)
+Não se preocupe, é só minha cota. Embora uma escritura de terra pareça uma boa coisa de se ter, duvido que alguém ligue hoje em dia. Jogue na fogueira, se quiser. </t>
         </is>
       </c>
     </row>
@@ -903,11 +901,10 @@
 To celebrate your new beginning, I will give you a hatchet. It will be of great use to you as you work your way through the land.</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Parabéns, a terra agora é sua._x000D_
-_x000D_
-Para celebrar o seu novo começo, vou te dar um machado. Ele será de grande utilidade enquanto você desbrava a terra.</t>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>Parabéns, a terra agora é sua.
+Para celebrar o novo começo, vou te dar um machado. Será de grande utilidade enquanto você abre caminho pela terra.</t>
         </is>
       </c>
     </row>
@@ -940,13 +937,11 @@
 Fiama carries some beginner home furnishings in custody, so don't forget to buy them.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>E estes são 10 barras de ouro, os suprimentos de socorro fornecidos por Mysilia._x000D_
-_x000D_
-Barras de ouro são um recurso útil que pode ser usado para contratar moradores e também podem ser trocadas por diversos itens essenciais para o desenvolvimento do seu lar._x000D_
-_x000D_
-Fiama tem em custódia alguns móveis básicos para residência, então não se esqueça de comprá-los.</t>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>E estas são 10 barras de ouro, os suprimentos de ajuda fornecidos por Mysilia.
+Barras de ouro são um recurso útil que serve para contratar moradores e também podem ser trocadas por vários itens essenciais ao desenvolvimento do seu lar.
+A Fiama guarda alguns móveis iniciantes de lar, então não se esqueça de comprá-los.</t>
         </is>
       </c>
     </row>
@@ -976,9 +971,9 @@
           <t>We are going to stay here for a while longer and see how it develops. Hey, I feel a little responsible for having kindled your pioneering spirit.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Ficaremos aqui por mais um tempo e veremos como se desenvolve. Ei, sinto-me um pouco responsável por ter despertado o seu espírito pioneiro.</t>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>Vamos ficar por aqui mais um tempo e ver como se desenvolve. Ei, sinto um pouco de responsabilidade por ter aceso seu espírito pioneiro.</t>
         </is>
       </c>
     </row>
@@ -1009,9 +1004,9 @@
           <t>I posted some requests on the bulletin board. Take a look when you have time.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Postei alguns pedidos no mural de avisos. Dê uma olhada quando tiver um tempo.</t>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>Postei alguns pedidos no quadro de avisos. Dê uma olhada quando tiver tempo.</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1055,15 @@
       <c r="K49" s="17" t="inlineStr">
         <is>
           <t>Oh, that paper?
-That is a "land deed". Mysillia is looking for pioneers and we're giving away land for free to promising adventurers.
+That is a "land deed". Mysilia is looking for pioneers and we're giving away land for free to promising adventurers.
  ...Well, of course, houses and people don't just pop up from nowhere. You will be carving your way through bushes and there's no one to protect the land from rogues and vicious creatures. Eventually, you will have to pay taxes too.</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Oh, esse papel?_x000D_
-_x000D_
-Isso é uma "escritura de terra". Mysillia está em busca de pioneiros e estamos distribuindo terras gratuitamente para aventureiros promissores._x000D_
-_x000D_
- ...Bem, é claro que casas e pessoas não surgem do nada. Você irá abrir seu caminho através dos arbustos e não há ninguém para proteger a terra de bandidos e criaturas ferozes. Eventualmente, você também terá que pagar impostos.</t>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>Oh, aquele papel?
+É uma "escritura de terra". Mysilia está buscando pioneiros e estamos dando terras de graça para aventureiros promissores.
+...Bom, claro, casas e gente não brotam do nada. Você vai abrir caminho no mato e não haverá ninguém para proteger a terra de ladrões e criaturas maldosas. Eventualmente, terá de pagar impostos também.</t>
         </is>
       </c>
     </row>
@@ -1086,15 +1079,14 @@
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">I'm not going to lie. Fiama and I serve Mysillia and Mysillia needs allies and coins.
+          <t xml:space="preserve">I'm not going to lie. Fiama and I serve Mysillia and Mysilia needs allies and coins.
 So my secret intention here is to emphasize the favor we have done to you in a hope you might be driven to make a blooming town or two for us. (He grins at you gleefully) </t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não vou mentir. Fiama e eu servimos Mysillia, e Mysillia precisa de aliados e moedas._x000D_
-_x000D_
-Então, minha intenção secreta aqui é enfatizar o favor que fizemos a você, na esperança de que você seja impulsionado a construir uma ou duas cidades florescentes para nós. (Ele sorri para você com entusiasmo) </t>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não vou mentir. A Fiama e eu servimos a Mysilia e Mysilia precisa de aliados e moedas.
+Então minha intenção secreta aqui é enfatizar o favor que fizemos a você na esperança de que você se sinta movido a erguer uma cidadezinha florescente ou duas para nós. (Ele sorri para você, radiante) </t>
         </is>
       </c>
     </row>
@@ -1112,9 +1104,9 @@
           <t>This place actually doesn't look bad for a new settlement. Why don't you go find a good spot and read the deed?</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Este lugar, na verdade, não parece mal para um novo assentamento. Por que você não vai procurar um bom local e ler a escritura?</t>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>Este lugar, na real, não parece mau para um assentamento novo. Que tal encontrar um bom lugar e ler a escritura?</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1142,11 @@
 As long as you can pay us a certain amount of income, we won't have any say in the matter. Well, if you don't know where to start, take a look at the bulletin board. I've posted some requests for you to begin with.</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>O que você quer construir nesta terra?_x000D_
-_x000D_
-Um lugar para os viajantes descansarem suas asas, uma oficina de artesãos onde mestres artistas exercitam suas habilidades, ou uma pacata vila agrícola com espigas de trigo balançando... Se você tem uma visão para o futuro, esse é o seu "objetivo"._x000D_
-_x000D_
-Contanto que você possa nos pagar uma certa quantia de renda, não teremos interferência na questão. Bem, se você não sabe por onde começar, dê uma olhada no mural de avisos. Eu postei alguns pedidos para você começar.</t>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>O que você quer construir nesta terra?
+Um lugar para viajantes pousarem as asas, a oficina de um artesão onde artistas mestres exercitam seus talentos, ou uma vila agrícola pacífica com espigas de trigo balançando... Se você tem uma visão do futuro, esse é o seu "objetivo".
+Contanto que você pague uma certa renda, não temos nada a dizer sobre o assunto. Bom, se não sabe por onde começar, olhe o quadro de avisos. Postei alguns pedidos para você começar.</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1176,7 @@
           <t>What do you want to know?</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" s="12" t="inlineStr">
         <is>
           <t>O que você quer saber?</t>
         </is>
@@ -1216,9 +1206,9 @@
           <t>Who was the Elean girl I saw?</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Quem era a garota eleana que eu vi?</t>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>Quem era a garota Elea que eu vi?</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1236,7 @@
           <t>What is Nefia?</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="12" t="inlineStr">
         <is>
           <t>O que é Nefia?</t>
         </is>
@@ -1281,9 +1271,9 @@
           <t>About the current situation in Mysilia.</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Sobre a situação atual em Mysilia.</t>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>Sobre a situação atual de Mysilia.</t>
         </is>
       </c>
     </row>
@@ -1316,9 +1306,9 @@
           <t>About Lord Cetrus.</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Sobre Lord Cetrus.</t>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>Sobre o Lorde Cetrus.</t>
         </is>
       </c>
     </row>
@@ -1351,9 +1341,9 @@
           <t>About Human and Elea.</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Sobre Humanos e Elea.</t>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>Sobre humanos e Elea.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1376,7 @@
           <t>About House Torres.</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L66" s="12" t="inlineStr">
         <is>
           <t>Sobre a Casa Torres.</t>
         </is>
@@ -1416,7 +1406,7 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L67" s="12" t="inlineStr">
         <is>
           <t>(Voltar)</t>
         </is>
@@ -1455,7 +1445,7 @@
           <t>What do you want to learn?</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L74" s="12" t="inlineStr">
         <is>
           <t>O que você quer aprender?</t>
         </is>
@@ -1485,9 +1475,9 @@
           <t>Picking and using items.</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Selecionar e usar itens.</t>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>Pegando e usando itens.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1510,7 @@
           <t>Gathering and fatigue.</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" s="12" t="inlineStr">
         <is>
           <t>Coleta e fadiga.</t>
         </is>
@@ -1555,9 +1545,9 @@
           <t>Craft.</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Artesanato.</t>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>Fabricação.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1580,7 @@
           <t>Combat.</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L78" s="12" t="inlineStr">
         <is>
           <t>Combate.</t>
         </is>
@@ -1625,7 +1615,7 @@
           <t>Abilities and spells.</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L79" s="12" t="inlineStr">
         <is>
           <t>Habilidades e feitiços.</t>
         </is>
@@ -1660,7 +1650,7 @@
           <t>Eating, sleeping, living.</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L80" s="12" t="inlineStr">
         <is>
           <t>Comer, dormir, viver.</t>
         </is>
@@ -1695,7 +1685,7 @@
           <t>Field of view and light sources.</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L81" s="12" t="inlineStr">
         <is>
           <t>Campo de visão e fontes de luz.</t>
         </is>
@@ -1725,7 +1715,7 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L82" s="12" t="inlineStr">
         <is>
           <t>(Voltar)</t>
         </is>
@@ -1757,7 +1747,7 @@
           <t>Field of view and light sources.</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L84" s="12" t="inlineStr">
         <is>
           <t>Campo de visão e fontes de luz.</t>
         </is>
@@ -1807,12 +1797,12 @@
 Picking up items placed in towns requires the art of stealing, but there is no need to learn it for now.</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Primeiro, deixe-me te ensinar como pegar e usar itens.
-Itens no chão podem ser coletados automaticamente ao caminhar sobre eles, mas itens colocados, como móveis, devem primeiro ser segurados na mão ao clicar com o botão direito sobre eles.
-Quando você estiver segurando um item, pode clicar com o botão direito no chão para colocá-lo novamente. Ou clicar em si mesmo para guardá-lo na sua mochila.
-Pegar itens colocados em cidades requer a arte de roubo, mas não há necessidade de aprendê-la por agora.</t>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>Primeiro, deixe-me contar como pegar e usar itens.
+Itens no chão são pegos automaticamente ao passar por cima, mas itens colocados, como móveis, precisam primeiro ser segurados com o clique direito neles.
+Quando estiver segurando um item, clique com o botão direito no chão para colocá-lo de volta. Ou clique em você mesmo para pôr na mochila.
+Pegar itens colocados em cidades exige a arte do furto, mas não precisa aprendê-la por ora.</t>
         </is>
       </c>
     </row>
@@ -1830,15 +1820,15 @@
       <c r="K88" s="16" t="inlineStr">
         <is>
           <t>Click the inventory icon at the lower right corner of your screen to open your backpack. Items in your backpack can be moved freely by dragging.
-Items such as food and books can be used directly by right-clicking on them. You can also middle-click(or press R key) an item to display all actions you can perform on the item.
+Items such as food and books can be used directly by right-clicking on them. You can also middle-click (or press R key) an item to display all actions you can perform on the item.
 The slots in the lower screen toolbar can be easily swapped with the mouse wheel, making it easy to switch between frequently used items and tools.</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Clique no ícone do inventário no canto inferior direito da tela para abrir sua mochila. Os itens na sua mochila podem ser movidos livremente arrastando-os.
-Itens como comida e livros podem ser usados diretamente ao clicar com o botão direito sobre eles. Você também pode clicar com o botão do meio (ou pressionar a tecla R) em um item para exibir todas as ações que pode realizar com ele.
-Os espaços na barra de ferramentas inferior podem ser facilmente trocados com a roda do mouse, facilitando a alternância entre itens e ferramentas de uso frequente.</t>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>Clique no ícone de inventário no canto inferior direito da tela para abrir a mochila. Itens na mochila podem ser movidos livremente arrastando.
+Itens como comida e livros podem ser usados diretamente com o clique direito. Você também pode clicar com o botão do meio (ou apertar a tecla R) num item para mostrar todas as ações possíveis com ele.
+Os slots da barra inferior trocam fácil com a rodinha do mouse, o que facilita alternar entre itens e ferramentas de uso frequente.</t>
         </is>
       </c>
     </row>
@@ -1894,11 +1884,10 @@
 You can try to collect resources on the map by right-clicking on them. But note that some items require tools such as an axe or a pickaxe to harvest.</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Por enquanto, os recursos naturais serão essenciais para sua sobrevivência. Cogumelos selvagens e frutas são uma fonte valiosa de alimento. Você pode cortar árvores e processar pedras para fabricar móveis e construir edificações._x000D_
-_x000D_
-Você pode tentar coletar recursos no mapa clicando com o botão direito sobre eles. Mas note que alguns itens exigem ferramentas, como um machado ou uma picareta, para serem extraídos.</t>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>Por ora, os recursos naturais serão essenciais à sua vida. Cogumelos e frutinhas silvestres são fonte valiosa de comida. Você pode cortar árvores e processar pedras para fazer móveis e construções.
+Tente coletar recursos no mapa clicando com o botão direito neles. Mas repare: alguns itens exigem ferramentas como machado ou picareta para colher.</t>
         </is>
       </c>
     </row>
@@ -1920,13 +1909,11 @@
 If you are too tired to walk, a night's sleep in bed will relieve the fatigue. If you cannot find a bed, try using "Rest" ability.</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Certas atividades, como coletar, consomem sua energia. A regeneração natural para conforme sua fadiga se acumula, e há risco de desmaiar se continuar se movendo._x000D_
-_x000D_
-Existem poucas maneiras de se recuperar da fadiga, então tenha cuidado quando não estiver forte o suficiente._x000D_
-_x000D_
-Se estiver cansado demais para andar, uma noite de sono na cama aliviará a fadiga. Se não conseguir encontrar uma cama, tente usar a habilidade "Descansar".</t>
+      <c r="L94" s="12" t="inlineStr">
+        <is>
+          <t>Certas atividades, como coletar, consomem seu vigor. A cura natural cessa conforme a fadiga acumula, e há risco de desmaiar se continuar se mexendo.
+Há poucos jeitos de recuperar da fadiga, então cuidado quando não estiver forte o bastante.
+Se estiver cansado demais para andar, uma noite de sono na cama alivia a fadiga. Se não achar uma cama, tente usar a habilidade "Descansar".</t>
         </is>
       </c>
     </row>
@@ -1982,11 +1969,10 @@
 Initially, the range of items you can create is limited, but as you obtain new recipes through your journey, you'll be able to craft a variety of useful items.</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Instalações como fogueiras e bancadas de trabalho podem ser usadas para fabricar itens, desde que você tenha os ingredientes necessários._x000D_
-_x000D_
-Inicialmente, a variedade de itens que você pode criar é limitada, mas conforme obtém novas receitas durante sua jornada, poderá fabricar uma grande variedade de itens úteis.</t>
+      <c r="L99" s="12" t="inlineStr">
+        <is>
+          <t>Instalações como fogueiras e bancadas servem para fabricar itens se você tiver os ingredientes necessários.
+No começo, a gama de itens criáveis é limitada, mas conforme obtém receitas novas na jornada, poderá fabricar uma variedade de itens úteis.</t>
         </is>
       </c>
     </row>
@@ -2006,10 +1992,10 @@
 If you lack the necessary crafting skills, you will consume a lot of stamina. So it is recommended that you first hone your skills by crafting simple items before trying high-level recipes.</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Ao fabricar itens, você pode usar ingredientes da sua Mochila, Caixas, Baús e de Contêineres distantes, desde que pertençam a você.
-Se você não tiver as habilidades necessárias para a criação, consumirá muita energia. Por isso, é recomendável aprimorar suas habilidades criando itens simples antes de tentar receitas de nível avançado.</t>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>Ao fabricar, você pode usar ingredientes da mochila e de contêineres distantes, contanto que lhe pertençam.
+Se faltarem as perícias de fabricação necessárias, você gastará muito vigor. Então recomendo primeiro lapidar as perícias fabricando itens simples antes de tentar receitas de nível alto.</t>
         </is>
       </c>
     </row>
@@ -2063,9 +2049,9 @@
           <t>(Coming!)</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>(Chegando!)</t>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>(Em breve!)</t>
         </is>
       </c>
     </row>
@@ -2121,9 +2107,9 @@
           <t>(Coming!)</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>(Chegando!)</t>
+      <c r="L111" s="12" t="inlineStr">
+        <is>
+          <t>(Em breve!)</t>
         </is>
       </c>
     </row>
@@ -2180,9 +2166,9 @@
           <t>(Coming!)</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>(Chegando!)</t>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>(Em breve!)</t>
         </is>
       </c>
     </row>
@@ -2238,9 +2224,9 @@
           <t>(Coming!)</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>(Chegando!)</t>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>(Em breve!)</t>
         </is>
       </c>
     </row>
@@ -2279,11 +2265,10 @@
 Ah, you must've seen Fiama in a daze. She's still here somewhere. She's the one who found you when you collapsed.</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>O quê, você viu uma garota Elean na floresta?_x000D_
-_x000D_
-Ah, você deve ter visto Fiama distraída. Ela ainda está por aqui em algum lugar. Foi ela quem te encontrou quando você desmaiou.</t>
+      <c r="L134" s="12" t="inlineStr">
+        <is>
+          <t>Como, você viu uma garota Elea no bosque?
+Ah, você deve ter visto a Fiama num daqueles devaneios dela. Ela ainda está por aqui em algum lugar. Foi ela quem te achou quando você desmaiou.</t>
         </is>
       </c>
     </row>
@@ -2303,11 +2288,10 @@
 She...hears the voice of forests. I recall she was muttering something strange while ago. That it was a girl in her dream which brought us here. I wonder what she meant.</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Fia é humana, mas você não foi o primeiro a se enganar._x000D_
-_x000D_
-Ela... ouve a voz das florestas. Lembro que há pouco tempo ela estava murmurando algo estranho. Que foi uma garota em seu sonho que nos trouxe até aqui. Me pergunto o que ela quis dizer.</t>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>A Fia é humana, mas você não é o primeiro a errar no palpite.
+Ela... ouve a voz das florestas. Lembro que ela ficava murmurando coisa estranha há pouco. Que foi uma garota em seu sonho que nos trouxe aqui. Fico me perguntando o que quis dizer.</t>
         </is>
       </c>
     </row>
@@ -2339,9 +2323,9 @@
           <t>There are many unexplored ruins scattered around in Tyris and we call them 'Nefia'. It is rumored that ancient treasures lie dormant in the depths of Nefia, but it would be wise to avoid rushing into exploration unless you consider yourself an adventurer with considerable skill.</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>Existem muitas ruínas inexploradas espalhadas por Tyris, e nós as chamamos de 'Nefia'. Dizem que tesouros antigos jazem adormecidos nas profundezas de Nefia, mas seria sensato evitar se aventurar nelas apressadamente, a menos que se considere um aventureiro de grande habilidade.</t>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>Há muitas ruínas inexploradas espalhadas por Tyris e as chamamos de 'Nefia'. Corre rumor de que tesouros antigos dormem nas profundezas das Nefia, mas é sensato evitar se aventurar às pressas, a menos que se considere um aventureiro de habilidade considerável.</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2361,10 @@
 Mysilia was not rich, but it was a peaceful land full of hope.</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Mysilia é um principado governado pelo velho Lorde Jonan, localizado na fronteira entre o Norte de Tyris e as montanhas do sul. Por muito tempo, humanos e Eleas viveram lado a lado._x000D_
-_x000D_
-Dizem que já se passaram cem anos desde que meu mestre, Lorde Cetrus, visitou estas terras como mensageiro de Vindale. Lorde Cetrus e sua esposa, Lady Frine, decidiram permanecer em nosso mundo humano e, por muito tempo, foram adorados pelo povo como um símbolo da coexistência entre as duas raças._x000D_
-_x000D_
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Mysilia é um principado governado pelo velho Lorde Jonan, situado na fronteira entre Tyris do Norte e as montanhas do sul. Por muito tempo, humanos e Eleas viveram de mãos dadas.
+Dizem que já faz cem anos que meu mestre, o Lorde Cetrus, visitou esta terra como mensageiro de Vindale. O Lorde Cetrus e sua Dama Frine decidiram permanecer no nosso mundo de humanos e há muito são adorados pelo povo como símbolo da convivência das duas raças.
 Mysilia não era rica, mas era uma terra pacífica e cheia de esperança.</t>
         </is>
       </c>
@@ -2407,11 +2389,11 @@
 That is the current state of the country.</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Mas a última guerra, que terminou há 15 anos, deixou cicatrizes profundas em Mysilia e na relação entre as duas raças.
-Vindale permaneceu em silêncio diante de nosso pedido e deixou Tyris ser invadida pelo império. A desconfiança que cresceu entre os humanos lançou uma sombra de conflito e amargura sobre Mysilia, que representava a harmonia entre as duas raças.
-A voz de Lorde Cetrus já não alcança mais os ouvidos do povo. Os abutres do país vizinho e o Congresso nos observam com sorrisos no rosto, enquanto nossos compatriotas brigam pelos últimos grãos de trigo na terra desolada.
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>Mas a última guerra, que acabou há 15 anos, deixou cicatrizes profundas em Mysilia e na relação entre as duas raças.
+Vindale ficou calado ao nosso pedido e deixou Tyris ser invadida pelo império. A desconfiança que cresceu entre os humanos lançou sombra de conflito e amargura sobre Mysilia, que representava a harmonia das duas raças.
+A voz do Lorde Cetrus já não alcança os ouvidos do povo. Os abutres do país vizinho e o Congresso nos observam sorrindo enquanto nossos compatriotas brigam pelas últimas espigas de trigo da terra desolada.
 Esse é o estado atual do país.</t>
         </is>
       </c>
@@ -2432,10 +2414,10 @@
 But it seems that Lord Cetrus has not given up yet. I, too, will do my best to the end for the country of my birth...no, for my master Cetrus.</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Talvez não haja mais esperança para Mysilia, e os dias em que humanos e Elea davam as mãos nunca mais voltem.
-Mas parece que Lorde Cetrus ainda não desistiu. Eu também darei o meu melhor até o fim, pelo país onde nasci... não, pelo meu mestre Cetrus.</t>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>Pode não haver esperança para Mysilia, e talvez os dias de humanos e Elea de mãos dadas nunca voltem.
+Mas parece que o Lorde Cetrus ainda não desistiu. Eu também farei o meu melhor até o fim pelo país onde nasci... não, pelo meu mestre Cetrus.</t>
         </is>
       </c>
     </row>
@@ -2469,11 +2451,10 @@
 Lord Cetrus and his Lady Frine came from Vindale. They have lived in Mysilia and have supported the House of Torres and the country for generations. He is a wise and well-liked man.</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Você deve ter ouvido rumores sobre ele. Senhor de Willow, Senhor da Fronteira, Filho da Outra Floresta e o herói de Nymelle. A lista continua._x000D_
-_x000D_
-Lorde Cetrus e sua esposa, Lady Frine, vieram de Vindale. Eles viveram em Mysilia e apoiaram a Casa de Torres e o país por gerações. Ele é um homem sábio e muito estimado.</t>
+      <c r="L149" s="12" t="inlineStr">
+        <is>
+          <t>Você deve ter ouvido os rumores dele. Lorde de Salgueiro, Senhor da Fronteira, Filho da Outra Floresta, e o herói de Nymelle. A lista segue.
+O Lorde Cetrus e sua Dama Frine vieram de Vindale. Vivem em Mysilia e apoiam a Casa Torres e o país há gerações. É um homem sábio e bem quisto.</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2476,10 @@
 We saw a ray of blue light over Nymelle. And then...</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Seus feitos na última Guerra dos Dez Anos ainda estão frescos na memória das pessoas. Aquele dia... aquela visão... ainda está gravada nas pálpebras de todo o povo de Mysilia._x000D_
-_x000D_
-Eu estava nas muralhas de Willow, olhando para o céu e amaldiçoando a aeronave Cyran que se aproximava de Mysilia, sem poder fazer nada. Lorde Cetrus havia se isolado desde a perda de Lady Frine, mas saiu de seu quarto exatamente quando todos no forte começaram a se reunir. Ele olhou tristemente para o céu e disse algo, em palavras Eleas, é claro._x000D_
-_x000D_
+      <c r="L150" s="12" t="inlineStr">
+        <is>
+          <t>Seus feitos na última Guerra dos Dez Anos ainda estão frescos na memória do povo. Aquele dia... aquela visão... ainda está gravada nas pálpebras de todo o povo de Mysilia.
+Eu estava nas muralhas de Salgueiro, olhando para o céu e xingando a aeronave Cyrana que se aproximava de Mysilia, sem poder fazer nada. O Lorde Cetrus estava recolhido desde a perda da Dama Frine, mas saiu do quarto justamente quando todos no forte começaram a se reunir. Olhou o céu com tristeza e disse algo, em palavras Elea, claro.
 Vimos um raio de luz azul sobre Nymelle. E então...</t>
         </is>
       </c>
@@ -2521,11 +2500,10 @@
 ...With the loss of Cyran airship, which had been called invincible, the empire began a gradual retreat from Tyris and the rest of the world. This was the end of the Ten Years' War.</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Não tenho palavras para descrever o que aconteceu naquele momento. Um vento azul varreu o céu e a aeronave Cyran foi engolida por uma tempestade furiosa. Depois que a tempestade passou, todos os presentes ficaram sem voz, apenas observando a luz vermelha enquanto ela ardia e caía lentamente. Quando olhei para meu senhor Cetrus, ele estava chorando._x000D_
-_x000D_
-...Com a perda da aeronave Cyran, que era considerada invencível, o império começou uma retirada gradual de Tyris e do resto do mundo. Esse foi o fim da Guerra dos Dez Anos.</t>
+      <c r="L151" s="12" t="inlineStr">
+        <is>
+          <t>Não tenho palavras para descrever o que aconteceu então. Um vento azul soprou pelo céu e a aeronave Cyrana foi engolida pela tempestade enfurecida. Depois que a tempestade passou, todos os presentes esqueceram as próprias vozes e ficaram apenas vendo a luz vermelha queimar e despencar lentamente. Quando vi meu Lorde Cetrus, ele estava chorando.
+...Com a perda da aeronave Cyrana, que chamavam de invencível, o império começou uma retirada gradual de Tyris e do resto do mundo. Esse foi o fim da Guerra dos Dez Anos.</t>
         </is>
       </c>
     </row>
@@ -2560,11 +2538,10 @@
 Elea is a beautiful, peaceful and docile race. They gave humans much knowledge, but did not actively seek to be involved. They lived in the blue forest and were rarely seen by humans. The trees in their forests emitted a poisonous miasma and stubbornly refused human intrusion...</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Os Elea existiam muito antes de os humanos construírem sua civilização. Nos tempos antigos, os humanos admiravam os Elea por seu conhecimento excepcional e poderes mágicos. Houve um tempo em que os chamavam de mães ou os veneravam como deuses._x000D_
-_x000D_
-Os Elea são uma raça bela, pacífica e dócil. Eles concederam muito conhecimento aos humanos, mas nunca buscaram envolvimento ativo. Viviam na floresta azul e raramente eram vistos por humanos. As árvores de suas florestas emitiam um miasma venenoso e resistiam obstinadamente à intrusão humana...</t>
+      <c r="L157" s="12" t="inlineStr">
+        <is>
+          <t>Os Elea existiam muito antes de o homem construir civilização. Na antiguidade, os humanos veneravam os Elea pelo conhecimento e poderes mágicos notáveis. Os humanos chegaram a chamá-los de mães ou a cultuá-los como deuses.
+Os Elea são uma raça bela, pacífica e mansa. Deram muito conhecimento aos humanos, mas não buscavam se envolver ativamente. Viviam na floresta azul e raramente eram vistos por humanos. As árvores de suas florestas exalavam um miasma venenoso e recusavam teimosamente a intrusão humana...</t>
         </is>
       </c>
     </row>
@@ -2586,13 +2563,11 @@
 And there behind the voice of hatred, is always a power-obsessed ruler's agenda. Yeah, welcome to the world of humans. </t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Como você sabe, as relações atuais entre as duas raças não são boas. Os humanos guardam ressentimento pelo silêncio dos Elea durante a Guerra dos Dez Anos. Alguns dizem que a presença dos Elea impediu a independência e criatividade humana._x000D_
-_x000D_
-Mas desde quando eles se tornaram aliados dos humanos, muito menos seus pais? Os humanos tomaram a liberdade de chamá-los de mães e agora ficam furiosos por se sentirem negligenciados. Eles apenas tentam justificar em voz alta o ressentimento que nasce de sua dependência egoísta e sentimento de inferioridade._x000D_
-_x000D_
-E por trás dessa voz de ódio, sempre há a agenda de um governante obcecado pelo poder. Pois é, bem-vindo ao mundo dos humanos.</t>
+      <c r="L158" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Como sabe, as relações atuais entre as duas raças não são boas. Os humanos guardam ressentimento do silêncio dos Elea na Guerra dos Dez Anos. Alguns dizem que a presença dos Elea atrapalhou a independência e a criatividade humanas.
+Mas desde quando no mundo eles viraram aliados dos humanos, quanto menos mães? O homem chamou-os de mãe por conta própria e agora se irrita porque se sente negligenciado. Estão apenas tentando justificar em voz alta o ressentimento que nasce da dependência egoísta e do senso de inferioridade deles.
+E por trás da voz de ódio, sempre há a agenda de um governante obcecado por poder. Pois é, bem-vindo ao mundo dos humanos. </t>
         </is>
       </c>
     </row>
@@ -2626,11 +2601,10 @@
 Lord Jonan...my father still smiles like a child in front of him. A smile he never shows to me or my brother.</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Lord Cetrus e Lady Frine são muito especiais para os membros da família Torres. Para nós, eles são como pais que nos observam crescer, sacerdotes que estarão conosco até o fim de nossas vidas, professores da história de Mysilia e amigos com quem compartilhamos nossas alegrias e tristezas._x000D_
-_x000D_
-Lord Jonan... meu pai ainda sorri como uma criança diante dele. Um sorriso que ele nunca mostra para mim ou meu irmão.</t>
+      <c r="L163" s="12" t="inlineStr">
+        <is>
+          <t>O Lorde Cetrus e a Dama Frine são muito especiais para os da família Torres. Para nós, são os pais que nos veem crescer, os sacerdotes que estarão conosco no fim da vida, os professores da história de Mysilia, e os amigos com quem dividimos alegrias e tristezas.
+O Lorde Jonan... meu pai ainda sorri como criança na frente dele. Um sorriso que nunca mostra para mim ou para meu irmão.</t>
         </is>
       </c>
     </row>
@@ -2649,9 +2623,9 @@
           <t>In the wide, cold, stone-built Mysilian court, even blood brothers sometimes feel like strangers. I was always strongly attracted to them as a child, as they were so close and supportive of each other. Laugh at me if you want, but where Lord Cetrus and Lady Frine were present, there was always perfect harmony.</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>No amplo e frio tribunal de pedra de Mysilia, até mesmo irmãos de sangue às vezes parecem estranhos. Quando criança, eu sempre fui fortemente atraído por eles, pois eram tão próximos e solidários um com o outro. Ria de mim se quiser, mas onde Lord Cetrus e Lady Frine estavam, sempre havia perfeita harmonia.</t>
+      <c r="L164" s="12" t="inlineStr">
+        <is>
+          <t>Na corte mysiliana, ampla, fria e de pedra, até irmãos de sangue às vezes se sentem estranhos. Eu sempre fui fortemente atraído por eles quando criança, pois eram tão próximos e se apoiavam tanto. Ria de mim se quiser, mas onde o Lorde Cetrus e a Dama Frine estavam, havia sempre harmonia perfeita.</t>
         </is>
       </c>
     </row>
@@ -2893,13 +2867,11 @@
 You will regularly receive tax bills. And be warned, those who fall behind on their taxes face a grim fate.</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>Me dói ter que diminuir seu entusiasmo agora que está ansioso para se estabelecer em seu novo lar, mas isso é algo que você acabará descobrindo de qualquer forma._x000D_
-_x000D_
-Essa terra certamente é sua, e você tem liberdade para fazer o que quiser com ela. No entanto, enquanto estiver dentro do território de Mysilia, todo bem presente nela, até mesmo o último animal do rebanho, deve ser registrado no livro de impostos._x000D_
-_x000D_
-Você receberá regularmente faturas de impostos. E fique avisado, aqueles que atrasam seus pagamentos enfrentam um destino sombrio.</t>
+      <c r="L209" s="12" t="inlineStr">
+        <is>
+          <t>Dói em mim estragar seu entusiasmo, já que você está ansioso para se instalar no novo lar, mas isto é algo que você aprenderá de qualquer jeito.
+Esta terra é certamente sua, e você é livre para fazer o que quiser com ela. Porém, contanto que exista dentro do território de Mysilia, todo bem nesta terra, até o último bicho do gado, deve constar no livro fiscal.
+Você receberá faturas de imposto regularmente. E fique avisado: quem fica para trás nos impostos enfrenta um destino sombrio.</t>
         </is>
       </c>
     </row>
@@ -2917,9 +2889,9 @@
           <t>...Well, it's going to be a while yet. Don't worry now, just keep developing your home.</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>...Bem, ainda vai levar um tempo. Não se preocupe agora, apenas continue desenvolvendo sua casa.</t>
+      <c r="L210" s="12" t="inlineStr">
+        <is>
+          <t>...Bom, ainda vai demorar. Não se preocupe agora, apenas continue desenvolvendo o lar.</t>
         </is>
       </c>
     </row>
@@ -2965,11 +2937,10 @@
 Let me explain how to pay your taxes. The payment method is simple, so don't worry about it. The important thing is whether you have the money available.</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>Vejo que você finalmente recebeu sua fatura._x000D_
-_x000D_
-Deixe-me explicar como pagar seus impostos. O método de pagamento é simples, então não se preocupe com isso. O importante é ter o dinheiro disponível.</t>
+      <c r="L216" s="12" t="inlineStr">
+        <is>
+          <t>Vejo que finalmente recebeu sua fatura.
+Deixe-me explicar como pagar os impostos. O método de pagamento é simples, não se preocupe. O importante é se você tem o dinheiro disponível.</t>
         </is>
       </c>
     </row>
@@ -2986,14 +2957,13 @@
       <c r="K217" s="16" t="inlineStr">
         <is>
           <t>Take the bill you received to the capital of Mysilia. There is a tax box in the town hall. There, you can drop off the bill along with the money you have been billed.
-It will be truely pleasant to have a weight lifted off your shoulders. Why don't you go to the market in Mysilia and buy some souvenirs after you paid your tax?</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Leve a fatura que recebeu até a capital de Mysilia. Há uma caixa de impostos na prefeitura. Lá, você pode depositar a fatura junto com o valor cobrado._x000D_
-_x000D_
-É realmente um alívio tirar esse peso dos ombros. Por que não passa no mercado de Mysilia e compra algumas lembranças depois de pagar seu imposto?</t>
+It will be truly pleasant to have a weight lifted off your shoulders. Why don't you go to the market in Mysilia and buy some souvenirs after you paid your tax?</t>
+        </is>
+      </c>
+      <c r="L217" s="12" t="inlineStr">
+        <is>
+          <t>Leve a fatura que recebeu à capital de Mysilia. Há um baú de impostos na prefeitura. Lá, você deposita a fatura junto com o dinheiro cobrado.
+Será verdadeiramente prazer ter um peso saindo dos ombros. Por que não vai ao mercado de Mysilia comprar lembranças depois de pagar o imposto?</t>
         </is>
       </c>
     </row>
@@ -3011,9 +2981,9 @@
           <t>You will receive bills in the future under various names, not only taxes. The method of payment is the same for all of them, so don't worry. Just be mindful of payment deadlines. Not only will overdue bills damage your reputation, but the authorities are always willing to use force, you know.</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>No futuro, você receberá faturas com diversos nomes, não apenas impostos. O método de pagamento será o mesmo para todas, então não se preocupe. Apenas fique atento aos prazos. Além de prejudicar sua reputação, contas atrasadas podem levar as autoridades a recorrerem à força, você sabe.</t>
+      <c r="L218" s="12" t="inlineStr">
+        <is>
+          <t>Você receberá faturas no futuro com vários nomes, não só impostos. O método de pagamento é o mesmo para todas, então não se preocupe. Apenas fique atento aos prazos. Faturas vencidas não só mancham sua reputação: as autoridades adoram usar a força, sabia.</t>
         </is>
       </c>
     </row>
@@ -3031,9 +3001,9 @@
           <t>Oh yes, I forgot to tell you the most important thing. You can get to Mysilia by following the road southeast. It's a bit far, but you can't get lost.</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>Ah, sim, quase esqueci de dizer o mais importante. Você pode chegar a Mysilia seguindo a estrada para sudeste. É um pouco longe, mas não tem como se perder.</t>
+      <c r="L219" s="12" t="inlineStr">
+        <is>
+          <t>Ah sim, esqueci de te contar a coisa mais importante. Dá para chegar a Mysilia seguindo a estrada para o sudeste. É um pouco longe, mas você não se perde.</t>
         </is>
       </c>
     </row>
@@ -3076,13 +3046,11 @@
 Now that you've paid your taxes, I have something wonderful for you. The "mailbox" is a convenient piece of furniture that will automatically store all the letters and bills that arrive at the home. This way, you won't miss any important news amongst the other items.</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>Ficou nervoso ao pagar impostos pela primeira vez?_x000D_
-_x000D_
-Não foi nada difícil, certo? Como eu disse, o importante é apenas se você pode pagar._x000D_
-_x000D_
-Agora que quitou seus impostos, tenho algo maravilhoso para você. A "caixa de correio" é um móvel prático que armazenará automaticamente todas as cartas e faturas que chegarem à sua casa. Assim, você não perderá nenhuma notícia importante entre os outros itens.</t>
+      <c r="L223" s="12" t="inlineStr">
+        <is>
+          <t>Estava nervoso com o primeiro pagamento de imposto?
+Não foi nada difícil, certo? Como eu disse, o importante é só se você pode pagar.
+Agora que pagou os impostos, tenho algo maravilhoso para você. A "caixa de correio" é um móvel prático que guarda automaticamente todas as cartas e faturas que chegam ao lar. Assim, você não perde nenhuma notícia importante no meio dos outros itens.</t>
         </is>
       </c>
     </row>
@@ -3116,11 +3084,10 @@
 Compared to the war-torn Asseria to the east, North Tyris was originally a peaceful continent. Separated by the Asserian Sea, even the empire with its invincible Cyran airships rarely traveled afar to this continent.</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Antes de falar sobre o Conselho, deixe-me primeiro dar uma aula entediante de história._x000D_
-_x000D_
-Comparado à Asseria, devastada pela guerra no leste, North Tyris era originalmente um continente pacífico. Separado pelo Mar de Asseria, até mesmo o império, com seus invencíveis dirigíveis Cyran, raramente viajava para este continente.</t>
+      <c r="L227" s="12" t="inlineStr">
+        <is>
+          <t>Antes de falar do Conselho, deixe-me dar primeiro uma chata aula de história.
+Comparada à Asseria destroçada pela guerra a leste, Tyris do Norte era originalmente um continente pacífico. Separadas pelo Mar de Asseria, até o império, com suas aeronaves Cyranas invencíveis, raramente viajava longe até este continente.</t>
         </is>
       </c>
     </row>
@@ -3140,11 +3107,10 @@
 At the council meeting, proposals submitted to the union were discussed. These range from major inter-national issues to minor issues such as aid to local villages. The almighty council members are the ones who hold the votes to approve or reject these proposals.</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>No entanto, à medida que o atrito entre o Novo Reino de Yerl e o Império se aprofundava, o conflito logo se espalhou para o resto do mundo, e as nações de Tyris precisaram se unir. Assim, a União de Tyris foi estabelecida sob a bandeira da paz e prosperidade de Tyris._x000D_
-_x000D_
-Na reunião do conselho, as propostas submetidas à união são discutidas. Elas variam desde grandes questões internacionais até problemas menores, como ajuda a vilarejos locais. Os todo-poderosos membros do conselho são os que detêm os votos para aprovar ou rejeitar essas propostas.</t>
+      <c r="L228" s="12" t="inlineStr">
+        <is>
+          <t>Porém, conforme o atrito entre o Novo Reino de Yerl e o Império se aprofundou, o conflito logo se espalhou pelo resto do mundo, e as nações de Tyris precisaram unir forças. Assim nasceu a União de Tyris sob a bandeira da paz e prosperidade de Tyris.
+Na reunião do conselho, propostas submetidas à união eram debatidas. Vão de grandes questões internacionais a assuntos menores, como ajuda a vilas locais. Os onipotentes conselheiros são os que seguram os votos para aprovar ou rejeitar essas propostas.</t>
         </is>
       </c>
     </row>
@@ -3164,11 +3130,10 @@
 So greet and talk to a council member if you ever see one.</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>À medida que continuar sua jornada, certamente encontrará membros do conselho. É importante para o futuro desenvolvimento de sua casa conhecê-los e conquistar seu apoio._x000D_
-_x000D_
-Portanto, cumprimente e converse com um membro do conselho se encontrar um.</t>
+      <c r="L229" s="12" t="inlineStr">
+        <is>
+          <t>Conforme sua jornada continuar, você certamente encontrará conselheiros. Para o desenvolvimento futuro do seu lar, é importante fazer a amizade deles e ganhar seu apoio.
+Então cumprimente e converse com um conselheiro se vir um.</t>
         </is>
       </c>
     </row>
@@ -3235,11 +3200,10 @@
 If you go southeast from here, you will find a cave called Nymelle. Monsters there shouldn't be so dangerous, at least in shallow layers. And there's...something that concerns me there. Are you interested in exploring the cave?</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>Tyris é um continente tão grande. Quando se acostumar a viver aqui, talvez queira sair e explorar a área ao redor._x000D_
-_x000D_
-Se seguir para sudeste daqui, encontrará uma caverna chamada Nymelle. Os monstros lá não devem ser tão perigosos, pelo menos nas camadas superficiais. E há...algo que me preocupa lá. Você tem interesse em explorar a caverna?</t>
+      <c r="L240" s="12" t="inlineStr">
+        <is>
+          <t>Tyris é um continente muito grande. Quando se acostumar a viver aqui, você pode querer sair e explorar os arredores.
+Se for para o sudeste daqui, encontrará uma caverna chamada Nymelle. Os monstros de lá não devem ser tão perigosos, pelo menos nas camadas rasas. E há... algo que me preocupa lá. Está interessado em explorar a caverna?</t>
         </is>
       </c>
     </row>
@@ -3273,13 +3237,11 @@
 Both of these tools are indispensable for adventure. Make the most of them.</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>Antes de sair para explorar, vou lhe dar esses pergaminhos._x000D_
-_x000D_
-O "Pergaminho de Evacuação" permite que você saia de Nefia e retorne à superfície. O "Pergaminho de Retorno" transportará você para o nível mais baixo de Nefia que visitou ou para sua casa._x000D_
-_x000D_
-Ambas essas ferramentas são indispensáveis para a aventura. Faça bom uso delas.</t>
+      <c r="L242" s="12" t="inlineStr">
+        <is>
+          <t>Antes de sair para explorar, vou te dar estes pergaminhos.
+O "Pergaminho de Evacuação" permite sair de uma Nefia e voltar à superfície. O "Pergaminho de Retorno" te transfere ao nível mais fundo da Nefia que já visitou ou ao seu lar.
+Ambas as ferramentas são indispensáveis para a aventura. Aproveite-as ao máximo.</t>
         </is>
       </c>
     </row>
@@ -3337,11 +3299,10 @@
 Oh, well, let's hear your story.</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>Você voltou. Fiquei preocupado quando Fia desapareceu de repente. Mas ela sempre faz isso..._x000D_
-_x000D_
-Ah, bem, vamos ouvir sua história.</t>
+      <c r="L249" s="12" t="inlineStr">
+        <is>
+          <t>Você voltou. Fiquei preocupado quando a Fia sumiu de repente. Mas ela faz isso o tempo todo...
+Bom, vamos ouvir sua história.</t>
         </is>
       </c>
     </row>
@@ -3409,11 +3370,10 @@
 No, I find that hard to believe but if you both saw it, it doesn't sound like a hallucination.</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>Uma... mariposa gigante...? Você está fumando vapores de crim?_x000D_
-_x000D_
-Não, acho difícil de acreditar, mas se vocês dois viram, então não parece ser uma alucinação.</t>
+      <c r="L254" s="12" t="inlineStr">
+        <is>
+          <t>Uma mariposa... gigante...? Você está fumando vapor de crim?
+Não, acho difícil acreditar, mas se vocês dois viram, não parece alucinação.</t>
         </is>
       </c>
     </row>
@@ -3431,9 +3391,9 @@
           <t>A crystal of ether lying in the depths of the earth. So that is the true nature of the mysterious power we have been searching for. And If the lady of the forest is telling the truth, there is another crystal lying in the southeastern ruins of Lysanas.</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>Um cristal de éter repousando nas profundezas da terra. Então essa é a verdadeira natureza do poder misterioso que estamos procurando. E se a senhora da floresta estiver dizendo a verdade, há outro cristal nas ruínas ao sudeste de Lysanas.</t>
+      <c r="L255" s="12" t="inlineStr">
+        <is>
+          <t>Um cristal de éter deitado nas profundezas da terra. Então essa é a verdadeira natureza do poder misterioso que buscamos. E se a senhora da floresta está dizendo a verdade, há outro cristal deitado nas ruínas de Lysanas, a sudeste.</t>
         </is>
       </c>
     </row>
@@ -3453,10 +3413,9 @@
 Lysanas then. It's probably worth looking into.</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>Não devemos confiar levianamente na palavra de um ser antigo como ela, mas temos que admitir que não há outra escolha._x000D_
-_x000D_
+      <c r="L256" s="12" t="inlineStr">
+        <is>
+          <t>Nunca devemos confiar levemente na palavra de um ser velho como ela, mas temos de admitir que não há outra escolha.
 Lysanas, então. Provavelmente vale a pena investigar.</t>
         </is>
       </c>
@@ -3479,12 +3438,10 @@
 Efrond Torres. Heir to Jonan Torres, the Duke of Mysilia. My spoiled brother.</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>...E tem outra coisa que está me incomodando._x000D_
-_x000D_
-Você disse que viu um cara com uma tatuagem horrível no pescoço? Se meu palpite estiver certo... não, é claro que estou certo, não pode haver outro como ele em toda Tyris._x000D_
-_x000D_
+      <c r="L257" s="12" t="inlineStr">
+        <is>
+          <t>...E há outra coisa me incomodando.
+Você diz que viu um cara com uma tatuagem horrível no pescoço? Se meu palpite está certo... não, claro que está, não pode haver outro cara como ele em toda Tyris.
 Efrond Torres. Herdeiro de Jonan Torres, o Duque de Mysilia. Meu irmão mimado.</t>
         </is>
       </c>
@@ -3507,13 +3464,11 @@
 I don't like this but this is my homework. I will investigate the matter along with the information of Lysanas.</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>Não faça essa cara de surpresa. Eu não faço mais parte da Casa Torres. Agora sou apenas um humilde servo do Lorde Cetrus._x000D_
-_x000D_
-De qualquer forma, por que Efrond, o herdeiro de Mysilia, está trabalhando com o império?_x000D_
-_x000D_
-Não gosto disso, mas essa é minha tarefa. Vou investigar essa questão junto com as informações sobre Lysanas.</t>
+      <c r="L258" s="12" t="inlineStr">
+        <is>
+          <t>Não faça essa cara de surpresa. Eu não faço mais parte da Casa Torres. Agora sou só um humilde servo do Lorde Cetrus.
+Enfim, por que Efrond, por que o herdeiro de Mysilia está trabalhando com o império?
+Não gosto disso, mas é minha tarefa de casa. Vou investigar o assunto junto com as informações de Lysanas.</t>
         </is>
       </c>
     </row>
@@ -3533,11 +3488,10 @@
 We are going back to Willow Keep to report to Lord Cetrus. It has been a pleasure being part of your new home.</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>...Achei que fosse um desvio terrível quando resgatamos você, mas que surpresa. Graças a você, agora tenho muitas novas informações para trabalhar._x000D_
-_x000D_
-Estamos voltando para Willow Keep para relatar ao Lorde Cetrus. Foi um prazer fazer parte do seu novo lar.</t>
+      <c r="L259" s="12" t="inlineStr">
+        <is>
+          <t>...Pensei que fosse um desvio terrível quando o resgatamos, mas que surpresa. Graças a você, agora tenho muita informação nova para trabalhar.
+Vamos voltar ao Forte Salgueiro para reportar ao Lorde Cetrus. Foi um prazer fazer parte do seu novo lar.</t>
         </is>
       </c>
     </row>
@@ -3559,13 +3513,11 @@
 Good bye and may the wind bless you.</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>Se... se você estiver interessado em explorar Lysanas, estaria disposto a visitar Willow Keep?_x000D_
-_x000D_
-Sem pressa, é claro. Você pode continuar desenvolvendo sua casa ou viajar para ver mais do mundo. Cabe a você decidir o que verá e quais marcas deixará neste mundo._x000D_
-_x000D_
-Adeus e que o vento te abençoe.</t>
+      <c r="L261" s="12" t="inlineStr">
+        <is>
+          <t>Se... se você tiver interesse em explorar Lysanas, aceitaria visitar o Forte Salgueiro?
+Sem pressão, claro. Pode continuar desenvolvendo seu lar, ou viajar e ver mais do mundo. Cabe a você decidir o que vai ver e que vestígios vai deixar neste mundo.
+Adeus, e que o vento te abençoe.</t>
         </is>
       </c>
     </row>
@@ -3616,9 +3568,9 @@
           <t>Crafting is an essential skill for life and adventure. I am not a specialist, but I will share with you what I know of craftsmanship.</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>Criar é uma habilidade essencial para a vida e para a aventura. Não sou um especialista, mas vou compartilhar com você o que sei sobre artesanato.</t>
+      <c r="L272" s="12" t="inlineStr">
+        <is>
+          <t>Fabricação é uma perícia essencial para a vida e a aventura. Não sou especialista, mas compartilho o que sei de artesanato.</t>
         </is>
       </c>
     </row>
@@ -3638,11 +3590,10 @@
 You can create a workbench on the spot using the "Quick Craft" ability you already know. First, gather logs by chopping down nearby trees, and then use "Quick Craft" to make the workbench.</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>Certo, vamos começar fazendo uma bancada de trabalho. A bancada de trabalho é um equipamento fundamental para a criação de itens e, com ela, você também pode fabricar pisos e paredes improvisadas para sua primeira casa._x000D_
-_x000D_
-Você pode criar uma bancada de trabalho no local usando a habilidade "Criação Rápida" que você já conhece. Primeiro, colete toras derrubando árvores próximas e, em seguida, use "Criação Rápida" para fabricar a bancada.</t>
+      <c r="L273" s="12" t="inlineStr">
+        <is>
+          <t>Muito bem, vamos começar fazendo uma bancada de trabalho. A bancada é um equipamento fundamental para fabricar, e com ela você também pode fabricar pisos e paredes improvisados para sua primeira casa.
+Você pode criar uma bancada na hora usando a habilidade "Fabricação Rápida" que já conhece. Primeiro, junte troncos cortando as árvores próximas, depois use "Fabricação Rápida" para fazer a bancada.</t>
         </is>
       </c>
     </row>
@@ -3660,9 +3611,9 @@
           <t>Be sure to set the completed workbench on an appropriate ground.</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>Certifique-se de posicionar a bancada de trabalho concluída em um terreno adequado.</t>
+      <c r="L274" s="12" t="inlineStr">
+        <is>
+          <t>Lembre de colocar a bancada pronta num chão apropriado.</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3659,10 @@
 Have you tried using the workbench yet? Initially, there may be only a few items you can craft, but you'll be able to craft a variety of items as you obtain new recipes.</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>Nada mal._x000D_
-_x000D_
-Você já tentou usar a bancada de trabalho? Inicialmente, pode haver apenas alguns itens que você pode criar, mas à medida que obtiver novas receitas, poderá fabricar uma variedade maior de itens.</t>
+      <c r="L280" s="12" t="inlineStr">
+        <is>
+          <t>Nada mau.
+Já tentou usar a bancada? No começo, talvez haja poucos itens criáveis, mas você poderá fabricar uma variedade conforme obtiver receitas novas.</t>
         </is>
       </c>
     </row>
@@ -3732,11 +3682,10 @@
 Having a light source allows you to see a bit even in the dark night. You can make a "Torch" from the workbench, so gather the materials from around here and give it a try.</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>Ok, estamos prontos para construir a casa, mas antes disso, devemos criar uma fonte de luz para nos prepararmos para a noite._x000D_
-_x000D_
-Ter uma fonte de luz permite que você enxergue um pouco mesmo na escuridão. Você pode fazer uma "Tocha" na bancada de trabalho, então reúna os materiais por aqui e experimente.</t>
+      <c r="L281" s="12" t="inlineStr">
+        <is>
+          <t>Ok, está tudo pronto para construir a casa, mas antes disso, deveríamos fabricar uma fonte de luz para nos preparar para a noite.
+Com uma fonte de luz, você enxerga um pouco mesmo na noite escura. Dá para fazer uma "Tocha" na bancada, então junte os materiais daqui por perto e tente.</t>
         </is>
       </c>
     </row>
@@ -3754,9 +3703,9 @@
           <t>The strings you'll need to make the torch can be crafted from vines at the workbench. And once you've crafted the torch, don't forget to equip it in your light source equipment slot.</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>As cordas que você precisará para fazer a tocha podem ser fabricadas a partir de cipós na bancada de trabalho. E depois de criar a tocha, não se esqueça de equipá-la no slot de equipamento de fonte de luz.</t>
+      <c r="L282" s="12" t="inlineStr">
+        <is>
+          <t>As cordas necessárias para a tocha se fabricam com trepadeiras na bancada. E quando fabricar a tocha, não esqueça de equipá-la no slot de fonte de luz.</t>
         </is>
       </c>
     </row>
@@ -3788,9 +3737,9 @@
           <t>Good, you've taken your first step as a crafter. There is still much to learn, but I will give you a goal now.</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t>Muito bem, você deu seu primeiro passo como artesão. Ainda há muito a aprender, mas agora vou lhe dar um objetivo.</t>
+      <c r="L287" s="12" t="inlineStr">
+        <is>
+          <t>Bom, você deu seu primeiro passo como artesão. Ainda há muito a aprender, mas vou te dar um objetivo agora.</t>
         </is>
       </c>
     </row>
@@ -3810,10 +3759,10 @@
 It may sound like a lot of work, but if you enclose some space with walls and equip it with doors, you can probably call it a house. I'll prepare some housewarming gifts meanwhile. Go ahead and start building your house.</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t>O objetivo é: "Construir uma casa em sua terra por conta própria".
-Pode parecer muito trabalho, mas se você fechar um espaço com paredes e instalar portas, já pode chamá-lo de casa. Enquanto isso, vou preparar alguns presentes de boas-vindas. Vá em frente e comece a construir sua casa.</t>
+      <c r="L288" s="12" t="inlineStr">
+        <is>
+          <t>O objetivo é: "Construa uma casa na sua terra por conta própria".
+Pode parecer trabalhão, mas se fechar um espaço com paredes e instalar portas, dá para chamar de casa. Enquanto isso, preparo presentes de casa nova. Vá em frente e comece a construir.</t>
         </is>
       </c>
     </row>
@@ -3845,9 +3794,9 @@
           <t>Looks like your house is finished. Congratulations! Now you don't have to worry about staying out in the open exposed to the wind and rain.</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>Parece que sua casa está pronta. Parabéns! Agora você não precisa mais se preocupar em ficar ao ar livre exposto ao vento e à chuva.</t>
+      <c r="L292" s="12" t="inlineStr">
+        <is>
+          <t>Parece que sua casa está pronta. Parabéns! Agora não precisa mais se preocupar em ficar ao relente, exposto ao vento e à chuva.</t>
         </is>
       </c>
     </row>
@@ -3869,13 +3818,11 @@
 It's not much, but I'll give you a house plate and a room plate. Customize your new house to your heart's content.</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>Agora, deixe-me explicar um pouco sobre as casas._x000D_
-_x000D_
-A aparência e a função da casa que você constrói podem ser personalizadas usando placas de casa. Além disso, quando você divide o espaço interno da casa com paredes, você cria cômodos. Cada cômodo pode ser então personalizado usando placas de cômodo._x000D_
-_x000D_
-Não é muito, mas vou lhe dar uma placa de casa e uma placa de cômodo. Personalize sua nova casa como quiser.</t>
+      <c r="L293" s="12" t="inlineStr">
+        <is>
+          <t>Agora, deixe-me explicar um pouco sobre casas.
+A aparência e a função da casa que você constrói podem ser personalizadas com placas de casa. E quando você divide o espaço interno com paredes, cria cômodos. Cada cômodo pode então ser personalizado com placas de cômodo.
+Não é muita coisa, mas vou te dar uma placa de casa e uma de cômodo. Personalize sua casa nova à vontade.</t>
         </is>
       </c>
     </row>
@@ -3916,11 +3863,10 @@
 Many of the creatures you will encounter in the field will attack you on sight. You can see the strength of the enemy by hovering your mouse over the target. It is wise to avoid fighting strong enemies until you are well equipped.</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>Não faz mal aprender a manejar uma ou duas armas nestes tempos difíceis._x000D_
-_x000D_
-Muitas das criaturas que você encontrará no campo irão atacá-lo assim que o virem. Você pode ver a força do inimigo passando o mouse sobre o alvo. É prudente evitar lutar contra inimigos fortes até estar bem equipado.</t>
+      <c r="L299" s="12" t="inlineStr">
+        <is>
+          <t>Nunca é demais aprender a lidar com uma arma ou duas em tempos conturbados.
+Muitas das criaturas que você encontrar no campo atacam à vista. Você vê a força do inimigo passando o mouse sobre o alvo. É sensato evitar lutar com inimigos fortes até estar bem equipado.</t>
         </is>
       </c>
     </row>
@@ -3940,11 +3886,10 @@
 Now, don't be shy, go beat up those punks to your heart's content.</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>Primeiro, um rápido treino prático. Tenho um encrenqueiro amarrado atrás do quadro de avisos. Uma criatura não pode se mover quando está imobilizada, então mantenha distância e espere sua vida se recuperar caso esteja em perigo._x000D_
-_x000D_
-Agora, não tenha vergonha, vá espancar esses encrenqueiros à vontade.</t>
+      <c r="L300" s="12" t="inlineStr">
+        <is>
+          <t>Primeiro, um treino prático rápido. Tenho um punk qualquer amarrado atrás do quadro de avisos. Uma criatura não se mexe quando presa, então mantenha distância e espere a vida recuperar se estiver em perigo.
+Agora, sem timidez: vá espancar esses punks à vontade.</t>
         </is>
       </c>
     </row>
@@ -4002,11 +3947,10 @@
 Stupid enemies like punks are not scary because they only launch simple attacks. However, there are enemies that attack from range or enemies that have troublesome abilities if you attack them directly.</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>Muito bem._x000D_
-_x000D_
-Inimigos tolos como encrenqueiros não são assustadores porque só realizam ataques simples. No entanto, existem inimigos que atacam à distância ou que possuem habilidades problemáticas se você os enfrentar diretamente.</t>
+      <c r="L306" s="12" t="inlineStr">
+        <is>
+          <t>Bem feito.
+Inimigos toscos como punks não assustam porque só dão ataques simples. Porém, há inimigos que atacam de longe ou com habilidades chatas se você os atacar de frente.</t>
         </is>
       </c>
     </row>
@@ -4028,13 +3972,11 @@
 For such an opponent, long-range attacks are essential. I'll give you several tools, so try to defeat the boar with some ingenuity. Remember, the items can be "thrown".</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>O próximo alvo do treinamento é um javali selvagem. Mais uma vez, amarrei um atrás do quadro de avisos._x000D_
-_x000D_
-Assim como os encrenqueiros, os javalis são adversários simples, mas a habilidade de combate de animais selvagens não deve ser subestimada. Se você se aproximar demais, provavelmente acabará levando um golpe pelas costas._x000D_
-_x000D_
-Para esse tipo de oponente, ataques à distância são essenciais. Vou lhe dar algumas ferramentas, então tente derrotar o javali com um pouco de criatividade. Lembre-se, os itens podem ser "lançados".</t>
+      <c r="L307" s="12" t="inlineStr">
+        <is>
+          <t>O próximo alvo de treino é um javali selvagem. De novo, deixei um amarrado atrás do quadro de avisos.
+Como o punk, um javali é um oponente simples, mas a capacidade de luta dos animais selvagens não se subestima. Se entrar num corpo a corpo, provavelmente vai levar nas costas.
+Para tal oponente, ataques à distância são essenciais. Vou te dar várias ferramentas: tente derrotar o javali com criatividade. Lembre: itens podem ser "arremessados".</t>
         </is>
       </c>
     </row>
@@ -4080,11 +4022,10 @@
 Opponents like wild boars are relatively easy to deal with, but they can surround you, cut off your retreat, or even leave you stranded depending on the situation. It is important not to be overconfident and to have the means to leave the battle at any time.</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>Brilhante. Agora você não terá mais problemas com oponentes que simplesmente avançam contra você com força bruta._x000D_
-_x000D_
-Oponentes como javalis selvagens são relativamente fáceis de enfrentar, mas podem cercá-lo, cortar sua rota de fuga ou até deixá-lo encurralado, dependendo da situação. É importante não ser excessivamente confiante e sempre ter um meio de sair da batalha a qualquer momento.</t>
+      <c r="L312" s="12" t="inlineStr">
+        <is>
+          <t>Brilhante. Agora você não tem mais problema com oponentes que só te empurram na força bruta.
+Oponentes como javalis são relativamente fáceis, mas podem te cercar, cortar sua retirada, ou até deixar você encurralado dependendo da situação. É importante não ser arrogante e ter meios de sair da batalha a qualquer momento.</t>
         </is>
       </c>
     </row>
@@ -4106,13 +4047,11 @@
 North Tyris is full of dangerous monsters and rogues. You will have no difficulty finding a hundred or two hundred of them. The number of enemies you have defeated is tracked in the journal, so check it if you lost your count.</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>Para o seu treinamento avançado, vou estabelecer um objetivo para você._x000D_
-_x000D_
-O objetivo é..."Derrote cem inimigos, não importa quais sejam"._x000D_
-_x000D_
-O Norte de Tyris está repleto de monstros perigosos e bandidos. Você não terá dificuldade em encontrar cem ou duzentos deles. O número de inimigos que você derrotou é registrado no diário, então verifique se perder a conta.</t>
+      <c r="L313" s="12" t="inlineStr">
+        <is>
+          <t>Para continuar seu treino, vou te dar um objetivo.
+O objetivo é... "Derrote cem inimigos, sejam eles o que forem".
+Tyris do Norte está cheia de monstros e ladrões perigosos. Você não terá dificuldade de achar cem ou duzentos. O número de inimigos derrotados fica anotado no diário, confira lá se perder a conta.</t>
         </is>
       </c>
     </row>
@@ -4155,13 +4094,11 @@
 You can pay them to skill trainers to train or learn new skills in town.</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>Muito bem. Agora você já pode, pelo menos, se proteger._x000D_
-_x000D_
-Ainda há muito a aprender, mas, por enquanto, tente ganhar mais experiência no mundo real. Aqui estão algumas moedas de platina como recompensa._x000D_
-_x000D_
-Você pode usá-las para pagar treinadores de habilidades na cidade e aprender novas técnicas.</t>
+      <c r="L318" s="12" t="inlineStr">
+        <is>
+          <t>Muito bem. Agora você pode pelo menos se proteger.
+Ainda há muito a aprender, mas por ora, tente ganhar mais experiência prática. Aqui vão algumas moedas de platina de recompensa.
+Você paga com elas aos treinadores de perícia para treinar ou aprender perícias novas na cidade.</t>
         </is>
       </c>
     </row>
@@ -4195,10 +4132,10 @@
 The shared container is a vital piece of equipment for your residents to live and work in. Listen carefully as I'm only going to explain it once.</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>Enquanto constrói sua base aqui, você precisa conhecer o "Caixa Compartilhada".
-O container compartilhado é um item essencial para que seus moradores possam viver e trabalhar. Preste atenção, pois vou explicar apenas uma vez.</t>
+      <c r="L324" s="12" t="inlineStr">
+        <is>
+          <t>Conforme constrói sua base aqui, você precisa conhecer o "contêiner compartilhado".
+O contêiner compartilhado é um equipamento vital para os moradores viverem e trabalharem. Escute com atenção, porque só vou explicar uma vez.</t>
         </is>
       </c>
     </row>
@@ -4218,10 +4155,10 @@
 Shared containers are accessible to residents and party members. Those who are hungry will scavenge for food in the containers, and if they find good equipment, they may take it out. If there are materials needed for work, they will be consumed automatically.</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
-        <is>
-          <t>Armazenamentos como Caixotes, Baús e Barris possuem um sistema de "permissões". Normalmente, apenas você pode mover itens dentro e fora de um contêiner, mas é possível transformá-lo em um container compartilhado clicando no ícone de "Cadeado" no lado direito do contêiner.
-Os containers compartilhados podem ser acessados pelos moradores e membros do grupo. Quem estiver com fome poderá procurar comida neles e, se encontrar um bom equipamento, pode pegá-lo. Caso haja materiais necessários para o trabalho, eles serão consumidos automaticamente.</t>
+      <c r="L325" s="12" t="inlineStr">
+        <is>
+          <t>Contêineres como caixotes e barris têm o conceito de "permissões". Normalmente, só você move itens para dentro e fora de um contêiner, mas pode transformá-lo num contêiner compartilhado clicando no ícone de "Cadeado" à direita do contêiner.
+Contêineres compartilhados são acessíveis a moradores e membros do grupo. Quem estiver com fome fareja comida nos contêineres, e se achar equipamento bom, pode levá-lo. Se houver materiais necessários ao trabalho, serão consumidos automaticamente.</t>
         </is>
       </c>
     </row>
@@ -4241,11 +4178,10 @@
 I'll go ahead and give you this box which is a reward for this quest. Set it on the ground and try to turn it into a "shared container".</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>Além disso, fique atento à capacidade restante do container compartilhado, pois os moradores podem entregar produtos de trabalho ou itens que encontrarem._x000D_
-_x000D_
-Vou te dar esta caixa como recompensa por esta missão. Coloque-a no chão e tente transformá-la em um "Caixa Compartilhada".</t>
+      <c r="L326" s="12" t="inlineStr">
+        <is>
+          <t>Também fique de olho na capacidade restante do contêiner compartilhado, pois os moradores podem entregar produtos do trabalho ou coisas que acharam.
+Vou logo te dar esta caixa, que é a recompensa desta missão. Coloque-a no chão e tente transformá-la num "contêiner compartilhado".</t>
         </is>
       </c>
     </row>
@@ -4310,11 +4246,10 @@
 By changing the settings of the containers, you can also create containers that are used on a priority basis or containers that only allow items of a certain category to be moved in and out. You can try this out later when you need to organize the base's supplies.</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>Parece que você configurou um container compartilhado com sucesso._x000D_
-_x000D_
-Ao alterar as configurações dos containers, você também pode criar containers que são usados com prioridade ou que permitem apenas a movimentação de itens de uma determinada categoria. Você pode testar isso mais tarde, quando precisar organizar os suprimentos da base.</t>
+      <c r="L335" s="12" t="inlineStr">
+        <is>
+          <t>Parece que você configurou um contêiner compartilhado com sucesso.
+Mudando as configurações dos contêineres, você também pode criar contêineres de uso prioritário ou contêineres que só permitem itens de certa categoria entrarem e saírem. Experimente depois, quando precisar organizar os suprimentos da base.</t>
         </is>
       </c>
     </row>
@@ -4363,11 +4298,10 @@
 I haven't mentioned this, but it's customary to have a frontier inspector in Mysilian colonies. 'Inspector' may sound strict, but no need to worry. They're more like helpers who assist with your land's development.</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>Você chegou em um bom momento._x000D_
-_x000D_
-Eu ainda não mencionei isso, mas é costume ter um inspetor de fronteira nas colônias Mysilian. 'Inspetor' pode soar rigoroso, mas não se preocupe. Eles são mais como ajudantes que auxiliam no desenvolvimento da sua terra.</t>
+      <c r="L342" s="12" t="inlineStr">
+        <is>
+          <t>Você chegou numa boa hora.
+Não mencionei isto, mas é costume haver um inspetor de fronteira nas colônias mysilianas. 'Inspetor' pode soar severo, mas sem preocupação. São mais como ajudantes que assistem o desenvolvimento da sua terra.</t>
         </is>
       </c>
     </row>
@@ -4387,11 +4321,10 @@
 The choice is yours. What say you?</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>Bem, se você prefere viver livremente sem nenhuma interferência desnecessária, posso resolver isso em Mysilia para você._x000D_
-_x000D_
-A escolha é sua. O que me diz?</t>
+      <c r="L343" s="12" t="inlineStr">
+        <is>
+          <t>Bom, se preferir viver livre sem intromissões desnecessárias, posso arranjar as coisas em Mysilia para você.
+A escolha é sua. Que tal?</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4352,7 @@
           <t>I want the help of a frontier inspector.</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
+      <c r="L344" s="12" t="inlineStr">
         <is>
           <t>Quero a ajuda de um inspetor de fronteira.</t>
         </is>
@@ -4449,9 +4382,9 @@
           <t>I want to live as I please.</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>Quero viver como eu quiser.</t>
+      <c r="L345" s="12" t="inlineStr">
+        <is>
+          <t>Quero viver do meu jeito.</t>
         </is>
       </c>
     </row>
@@ -4498,11 +4431,10 @@
 Allow me to introduce my friend, and the finest frontier inspector in Mysilia, Loytel.</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>Eu imaginei que você diria isso. Na verdade, chamei um inspetor excelente que conheço para sua terra. Ele tem uma personalidade um pouco difícil, mas faz um trabalho impecável._x000D_
-_x000D_
-Permita-me apresentar meu amigo, e o melhor inspetor de fronteira de Mysilia, Loytel.</t>
+      <c r="L349" s="12" t="inlineStr">
+        <is>
+          <t>Imaginei que diria isso. Na verdade, chamei um inspetor excelente que conheço para a sua terra. É um pouco difícil de personalidade, mas o trabalho dele é sólido.
+Deixe-me apresentar meu amigo, e o melhor inspetor de fronteira de Mysilia: Loytel.</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4457,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="L350" s="12" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4550,9 +4482,9 @@
           <t>...What is this?</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>...O que é isso?</t>
+      <c r="L351" s="12" t="inlineStr">
+        <is>
+          <t>...O que é isto?</t>
         </is>
       </c>
     </row>
@@ -4577,11 +4509,10 @@
 This is nothing but an unprepared, godforsaken, bloody wilderness!</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>'Uma terra promissora onde moedas voariam por toda parte', foi o que você disse, então eu vim... Eu ouvi errado?_x000D_
-_x000D_
-Isso aqui não passa de um deserto impreparado, esquecido pelos deuses e cheio de mato!</t>
+      <c r="L352" s="12" t="inlineStr">
+        <is>
+          <t>'Uma terra promissora onde moedas voarão por todo lado', você disse, então vim... Ouvi errado?
+Isto não passa de um maldito ermo impreparável, abandonado por Deus!</t>
         </is>
       </c>
     </row>
@@ -4604,9 +4535,9 @@
           <t>I demand a proper explanation, Ashland. I'm a busy man. What's the meaning of this? Why have you called me to this wilderness full of grass and rocks?</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>Exijo uma explicação adequada, Ashland. Sou um homem ocupado. O que significa isso? Por que me chamou para este fim de mundo cheio de grama e pedras?</t>
+      <c r="L353" s="12" t="inlineStr">
+        <is>
+          <t>Exijo uma explicação decente, Ashland. Sou um homem ocupado. Que significado tem isto? Por que me chamaram a este ermo cheio de mato e pedras?</t>
         </is>
       </c>
     </row>
@@ -4626,11 +4557,10 @@
 Indeed, this place is as dull as you say, but have you seen the face of this adventurer standing beside me? #He is the reason I've called you here.</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>Ah, Loytel, talvez sua longa jornada tenha turvado sua visão. Uma mina de ouro não fica simplesmente espalhada pelo chão._x000D_
-_x000D_
-De fato, este lugar é tão monótono quanto você diz, mas já viu o rosto deste aventureiro ao meu lado? #Ele é a razão de eu ter chamado você aqui.</t>
+      <c r="L354" s="12" t="inlineStr">
+        <is>
+          <t>Ah, Loytel, talvez sua viagem cansativa tenha turvado seus olhos. Uma mina de ouro não fica simplesmente deitada no chão.
+De fato, este lugar é tão monótono quanto você diz, mas já viu o rosto deste aventureiro ao meu lado? #Ele é a razão pela qual te chamei aqui.</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4583,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
+      <c r="L355" s="12" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4678,7 +4608,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
+      <c r="L356" s="12" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4698,7 +4628,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
+      <c r="L357" s="12" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -4723,9 +4653,9 @@
           <t>You're telling me this clueless-looking adventurer is the 'gold mine'?</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>Está me dizendo que este aventureiro com cara de perdido é a 'mina de ouro'?</t>
+      <c r="L358" s="12" t="inlineStr">
+        <is>
+          <t>Está me dizendo que este aventureiro de cara perdida é a 'mina de ouro'?</t>
         </is>
       </c>
     </row>
@@ -4743,9 +4673,9 @@
           <t>...Yes, that's right.</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>...Sim, exatamente.</t>
+      <c r="L359" s="12" t="inlineStr">
+        <is>
+          <t>...Sim, é isso.</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4700,10 @@
 But, good grief, this is really just a wild land as far as the eye can see. Normally, one would prepare adequately before embarking on a new land, you know?</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>Hmph, se você insiste tanto, suponho que posso aceitar o trabalho. Não estou particularmente empolgado, mas devo um grande favor a você e a Fia._x000D_
-_x000D_
-Mas, francamente, isto aqui é apenas um pedaço de terra selvagem até onde a vista alcança. Normalmente, alguém se prepararia adequadamente antes de embarcar em uma nova terra, sabia?</t>
+      <c r="L360" s="12" t="inlineStr">
+        <is>
+          <t>Hmph, se insiste tanto, acho que aceito o trabalho. Não estou particularmente entusiasmado, mas devo muito a você e à Fia.
+Mas, meus bons, isto é mesmo uma terra selvagem até onde a vista alcança. Normalmente, prepara-se direitinho antes de embarcar numa terra nova, sabia?</t>
         </is>
       </c>
     </row>
@@ -4801,13 +4730,11 @@
 With my experience and knowledge, this land is bound to succeed, though much depends on your effort, of course. Well, do your best.</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>Ahem... Bem, aventureiro, entendeu o recado?_x000D_
-_x000D_
-Vou me apresentar novamente. Sou Loytel, inspetor de fronteira de primeira classe de Mysilia, além de conselheiro da corte e oficial financeiro. Gosto de um bom vinho Olvina e de planos de desenvolvimento eficientes, e detesto pioneiros incompetentes._x000D_
-_x000D_
-Com minha experiência e conhecimento, esta terra certamente prosperará, embora muito dependa do seu esforço, é claro. Bem, faça o seu melhor.</t>
+      <c r="L361" s="12" t="inlineStr">
+        <is>
+          <t>Hem-hem... Bom, aventureiro, entendeu?
+Deixe-me me apresentar de novo. Sou Loytel, inspetor de fronteira de primeira classe de Mysilia, também servindo como conselheiro da corte e oficial financeiro. Gosto do bom vinho de Olvina e de planos de desenvolvimento eficientes, e detesto pioneiros incompetentes.
+Com minha experiência e conhecimento, esta terra vai vencer, embora muito dependa do seu esforço, claro. Bom, faça o seu melhor.</t>
         </is>
       </c>
     </row>
@@ -4827,11 +4754,10 @@
 If you're unsure about anything regarding the management of your home or life in Tyris, he's the one to consult.</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>Loytel pode ser rígido, mas é sincero. Ele certamente ajudará no desenvolvimento da sua terra._x000D_
-_x000D_
-Se tiver dúvidas sobre a administração do seu lar ou sobre a vida em Tyris, ele é a pessoa certa para consultar.</t>
+      <c r="L362" s="12" t="inlineStr">
+        <is>
+          <t>O Loytel pode ser severo, mas é sincero. Certamente ajudará no desenvolvimento da sua terra.
+Se tiver dúvida sobre qualquer coisa da administração do lar ou da vida em Tyris, é com ele que se fala.</t>
         </is>
       </c>
     </row>
@@ -4870,9 +4796,9 @@
           <t>Understood. If that's what you want, then do as you like. If you ever change your mind, feel free to talk to me again.</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>Entendido. Se é isso que você quer, então faça como desejar. Se algum dia mudar de ideia, sinta-se à vontade para falar comigo novamente.</t>
+      <c r="L371" s="12" t="inlineStr">
+        <is>
+          <t>Entendido. Se é o que você quer, faça como preferir. Se mudar de ideia, fale comigo de novo quando quiser.</t>
         </is>
       </c>
     </row>
